--- a/assets/templates/MII_master_template.xlsx
+++ b/assets/templates/MII_master_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\901810\GitHub\timesheet-generator\assets\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{495926E7-7BC2-4D1A-A818-CB8315FAC571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12F0763B-45E6-4E60-A91B-7CCEF3B1451F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -583,113 +583,113 @@
     <xf numFmtId="49" fontId="18" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1087,17 +1087,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="30" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="63" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -1105,15 +1105,15 @@
       <c r="L1" s="1"/>
     </row>
     <row r="2" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="31" t="s">
+      <c r="B2" s="51"/>
+      <c r="C2" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
@@ -1123,16 +1123,16 @@
       <c r="L2" s="1"/>
     </row>
     <row r="3" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="31" t="s">
+      <c r="B3" s="51"/>
+      <c r="C3" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -1141,10 +1141,10 @@
       <c r="L3" s="1"/>
     </row>
     <row r="4" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="29"/>
+      <c r="B4" s="51"/>
       <c r="C4" s="2" t="s">
         <v>4</v>
       </c>
@@ -1159,10 +1159,10 @@
       <c r="L4" s="1"/>
     </row>
     <row r="5" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="29"/>
+      <c r="B5" s="51"/>
       <c r="C5" s="2" t="s">
         <v>4</v>
       </c>
@@ -1170,21 +1170,21 @@
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="3"/>
-      <c r="H5" s="32" t="s">
+      <c r="H5" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="32"/>
+      <c r="I5" s="52"/>
       <c r="L5" s="1"/>
     </row>
     <row r="6" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="29"/>
-      <c r="C6" s="33" t="s">
+      <c r="B6" s="51"/>
+      <c r="C6" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="33"/>
+      <c r="D6" s="53"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="5" t="s">
@@ -1207,58 +1207,58 @@
       <c r="W6" s="8"/>
     </row>
     <row r="7" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="34" t="s">
+      <c r="A7" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="36" t="s">
+      <c r="B7" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="38" t="s">
+      <c r="C7" s="57"/>
+      <c r="D7" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="40" t="s">
+      <c r="E7" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="41"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="42"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="61"/>
+      <c r="H7" s="61"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="62"/>
       <c r="K7" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="L7" s="61" t="s">
+      <c r="L7" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="M7" s="61" t="s">
+      <c r="M7" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="N7" s="63" t="s">
+      <c r="N7" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="O7" s="61" t="s">
+      <c r="O7" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="P7" s="61" t="s">
+      <c r="P7" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="Q7" s="61" t="s">
+      <c r="Q7" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="R7" s="63" t="s">
+      <c r="R7" s="31" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:23" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="35"/>
+      <c r="A8" s="55"/>
       <c r="B8" s="22" t="s">
         <v>21</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="39"/>
+      <c r="D8" s="59"/>
       <c r="E8" s="22" t="s">
         <v>23</v>
       </c>
@@ -1278,17 +1278,17 @@
         <v>28</v>
       </c>
       <c r="K8" s="43"/>
-      <c r="L8" s="62"/>
-      <c r="M8" s="62"/>
-      <c r="N8" s="64"/>
-      <c r="O8" s="62"/>
-      <c r="P8" s="62"/>
-      <c r="Q8" s="62"/>
-      <c r="R8" s="64"/>
+      <c r="L8" s="30"/>
+      <c r="M8" s="30"/>
+      <c r="N8" s="32"/>
+      <c r="O8" s="30"/>
+      <c r="P8" s="30"/>
+      <c r="Q8" s="30"/>
+      <c r="R8" s="32"/>
     </row>
     <row r="9" spans="1:23" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="25">
-        <v>46143</v>
+        <v>46204</v>
       </c>
       <c r="B9" s="26">
         <v>0.33333333333333331</v>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="10" spans="1:23" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="25">
-        <v>46144</v>
+        <v>46205</v>
       </c>
       <c r="B10" s="26">
         <v>0.33333333333333331</v>
@@ -1346,7 +1346,7 @@
     </row>
     <row r="11" spans="1:23" s="15" customFormat="1" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="25">
-        <v>46145</v>
+        <v>46206</v>
       </c>
       <c r="B11" s="26">
         <v>0.33333333333333331</v>
@@ -1375,7 +1375,7 @@
     </row>
     <row r="12" spans="1:23" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="25">
-        <v>46146</v>
+        <v>46207</v>
       </c>
       <c r="B12" s="26">
         <v>0.33333333333333331</v>
@@ -1404,7 +1404,7 @@
     </row>
     <row r="13" spans="1:23" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="25">
-        <v>46147</v>
+        <v>46208</v>
       </c>
       <c r="B13" s="26">
         <v>0.33333333333333331</v>
@@ -1433,7 +1433,7 @@
     </row>
     <row r="14" spans="1:23" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="25">
-        <v>46148</v>
+        <v>46209</v>
       </c>
       <c r="B14" s="26">
         <v>0.33333333333333331</v>
@@ -1462,7 +1462,7 @@
     </row>
     <row r="15" spans="1:23" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="25">
-        <v>46149</v>
+        <v>46210</v>
       </c>
       <c r="B15" s="26">
         <v>0.33333333333333331</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="16" spans="1:23" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="25">
-        <v>46150</v>
+        <v>46211</v>
       </c>
       <c r="B16" s="26">
         <v>0.33333333333333331</v>
@@ -1520,7 +1520,7 @@
     </row>
     <row r="17" spans="1:18" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="25">
-        <v>46151</v>
+        <v>46212</v>
       </c>
       <c r="B17" s="26">
         <v>0.33333333333333298</v>
@@ -1549,7 +1549,7 @@
     </row>
     <row r="18" spans="1:18" s="15" customFormat="1" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="25">
-        <v>46152</v>
+        <v>46213</v>
       </c>
       <c r="B18" s="26">
         <v>0.33333333333333331</v>
@@ -1578,7 +1578,7 @@
     </row>
     <row r="19" spans="1:18" s="15" customFormat="1" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="25">
-        <v>46153</v>
+        <v>46214</v>
       </c>
       <c r="B19" s="26">
         <v>0.33333333333333331</v>
@@ -1607,7 +1607,7 @@
     </row>
     <row r="20" spans="1:18" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="25">
-        <v>46154</v>
+        <v>46215</v>
       </c>
       <c r="B20" s="26">
         <v>0.33333333333333331</v>
@@ -1636,7 +1636,7 @@
     </row>
     <row r="21" spans="1:18" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="25">
-        <v>46155</v>
+        <v>46216</v>
       </c>
       <c r="B21" s="26">
         <v>0.33333333333333331</v>
@@ -1665,7 +1665,7 @@
     </row>
     <row r="22" spans="1:18" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="25">
-        <v>46156</v>
+        <v>46217</v>
       </c>
       <c r="B22" s="26">
         <v>0.33333333333333331</v>
@@ -1694,7 +1694,7 @@
     </row>
     <row r="23" spans="1:18" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="25">
-        <v>46157</v>
+        <v>46218</v>
       </c>
       <c r="B23" s="26">
         <v>0.33333333333333331</v>
@@ -1723,7 +1723,7 @@
     </row>
     <row r="24" spans="1:18" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="25">
-        <v>46158</v>
+        <v>46219</v>
       </c>
       <c r="B24" s="26">
         <v>0.33333333333333298</v>
@@ -1752,7 +1752,7 @@
     </row>
     <row r="25" spans="1:18" s="15" customFormat="1" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="25">
-        <v>46159</v>
+        <v>46220</v>
       </c>
       <c r="B25" s="26">
         <v>0.33333333333333331</v>
@@ -1781,7 +1781,7 @@
     </row>
     <row r="26" spans="1:18" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="25">
-        <v>46160</v>
+        <v>46221</v>
       </c>
       <c r="B26" s="26">
         <v>0.33333333333333331</v>
@@ -1810,7 +1810,7 @@
     </row>
     <row r="27" spans="1:18" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="25">
-        <v>46161</v>
+        <v>46222</v>
       </c>
       <c r="B27" s="26">
         <v>0.33333333333333331</v>
@@ -1839,7 +1839,7 @@
     </row>
     <row r="28" spans="1:18" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="25">
-        <v>46162</v>
+        <v>46223</v>
       </c>
       <c r="B28" s="26">
         <v>0.33333333333333331</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="29" spans="1:18" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="25">
-        <v>46163</v>
+        <v>46224</v>
       </c>
       <c r="B29" s="26">
         <v>0.33333333333333331</v>
@@ -1897,7 +1897,7 @@
     </row>
     <row r="30" spans="1:18" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="25">
-        <v>46164</v>
+        <v>46225</v>
       </c>
       <c r="B30" s="26">
         <v>0.33333333333333298</v>
@@ -1926,7 +1926,7 @@
     </row>
     <row r="31" spans="1:18" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="25">
-        <v>46165</v>
+        <v>46226</v>
       </c>
       <c r="B31" s="26">
         <v>0.33333333333333298</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="32" spans="1:18" s="15" customFormat="1" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="25">
-        <v>46166</v>
+        <v>46227</v>
       </c>
       <c r="B32" s="26">
         <v>0.33333333333333331</v>
@@ -1984,7 +1984,7 @@
     </row>
     <row r="33" spans="1:18" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="25">
-        <v>46167</v>
+        <v>46228</v>
       </c>
       <c r="B33" s="26">
         <v>0.33333333333333331</v>
@@ -2013,7 +2013,7 @@
     </row>
     <row r="34" spans="1:18" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="25">
-        <v>46168</v>
+        <v>46229</v>
       </c>
       <c r="B34" s="26">
         <v>0.33333333333333298</v>
@@ -2042,7 +2042,7 @@
     </row>
     <row r="35" spans="1:18" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="25">
-        <v>46169</v>
+        <v>46230</v>
       </c>
       <c r="B35" s="26">
         <v>0.33333333333333298</v>
@@ -2071,7 +2071,7 @@
     </row>
     <row r="36" spans="1:18" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="25">
-        <v>46170</v>
+        <v>46231</v>
       </c>
       <c r="B36" s="26">
         <v>0.33333333333333298</v>
@@ -2100,7 +2100,7 @@
     </row>
     <row r="37" spans="1:18" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="25">
-        <v>46171</v>
+        <v>46232</v>
       </c>
       <c r="B37" s="26">
         <v>0.33333333333333298</v>
@@ -2129,7 +2129,7 @@
     </row>
     <row r="38" spans="1:18" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="25">
-        <v>46172</v>
+        <v>46233</v>
       </c>
       <c r="B38" s="26">
         <v>0.33333333333333298</v>
@@ -2158,7 +2158,7 @@
     </row>
     <row r="39" spans="1:18" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="25">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="B39" s="26">
         <v>0.33333333333333298</v>
@@ -2211,7 +2211,7 @@
         <v>0</v>
       </c>
       <c r="J40" s="9">
-        <f>COUNTIF(J9:J39,"x")</f>
+        <f>COUNTIF(J9:J39,"X")</f>
         <v>0</v>
       </c>
       <c r="K40" s="10"/>
@@ -2248,102 +2248,90 @@
       <c r="J42" s="50"/>
     </row>
     <row r="43" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="51" t="s">
+      <c r="A43" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="B43" s="52"/>
-      <c r="C43" s="53"/>
-      <c r="D43" s="51" t="s">
+      <c r="B43" s="34"/>
+      <c r="C43" s="35"/>
+      <c r="D43" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="E43" s="52"/>
-      <c r="F43" s="53"/>
-      <c r="G43" s="51" t="s">
+      <c r="E43" s="34"/>
+      <c r="F43" s="35"/>
+      <c r="G43" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="H43" s="52"/>
-      <c r="I43" s="52"/>
-      <c r="J43" s="53"/>
+      <c r="H43" s="34"/>
+      <c r="I43" s="34"/>
+      <c r="J43" s="35"/>
     </row>
     <row r="44" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="54"/>
-      <c r="B44" s="55"/>
-      <c r="C44" s="56"/>
-      <c r="D44" s="54"/>
-      <c r="E44" s="55"/>
-      <c r="F44" s="56"/>
-      <c r="G44" s="54"/>
-      <c r="H44" s="55"/>
-      <c r="I44" s="55"/>
-      <c r="J44" s="56"/>
+      <c r="A44" s="36"/>
+      <c r="B44" s="37"/>
+      <c r="C44" s="38"/>
+      <c r="D44" s="36"/>
+      <c r="E44" s="37"/>
+      <c r="F44" s="38"/>
+      <c r="G44" s="36"/>
+      <c r="H44" s="37"/>
+      <c r="I44" s="37"/>
+      <c r="J44" s="38"/>
     </row>
     <row r="45" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="54"/>
-      <c r="B45" s="55"/>
-      <c r="C45" s="56"/>
-      <c r="D45" s="54"/>
-      <c r="E45" s="55"/>
-      <c r="F45" s="56"/>
-      <c r="G45" s="54"/>
-      <c r="H45" s="55"/>
-      <c r="I45" s="55"/>
-      <c r="J45" s="56"/>
+      <c r="A45" s="36"/>
+      <c r="B45" s="37"/>
+      <c r="C45" s="38"/>
+      <c r="D45" s="36"/>
+      <c r="E45" s="37"/>
+      <c r="F45" s="38"/>
+      <c r="G45" s="36"/>
+      <c r="H45" s="37"/>
+      <c r="I45" s="37"/>
+      <c r="J45" s="38"/>
     </row>
     <row r="46" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="57"/>
-      <c r="B46" s="58"/>
-      <c r="C46" s="59"/>
-      <c r="D46" s="57"/>
-      <c r="E46" s="58"/>
-      <c r="F46" s="59"/>
-      <c r="G46" s="57"/>
-      <c r="H46" s="58"/>
-      <c r="I46" s="58"/>
-      <c r="J46" s="59"/>
+      <c r="A46" s="39"/>
+      <c r="B46" s="40"/>
+      <c r="C46" s="41"/>
+      <c r="D46" s="39"/>
+      <c r="E46" s="40"/>
+      <c r="F46" s="41"/>
+      <c r="G46" s="39"/>
+      <c r="H46" s="40"/>
+      <c r="I46" s="40"/>
+      <c r="J46" s="41"/>
       <c r="K46" s="11"/>
     </row>
     <row r="47" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="60" t="s">
+      <c r="A47" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="B47" s="60"/>
-      <c r="C47" s="60"/>
-      <c r="D47" s="60" t="s">
+      <c r="B47" s="42"/>
+      <c r="C47" s="42"/>
+      <c r="D47" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="E47" s="60"/>
-      <c r="F47" s="60"/>
-      <c r="G47" s="60" t="s">
+      <c r="E47" s="42"/>
+      <c r="F47" s="42"/>
+      <c r="G47" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="H47" s="60"/>
-      <c r="I47" s="60"/>
-      <c r="J47" s="60"/>
+      <c r="H47" s="42"/>
+      <c r="I47" s="42"/>
+      <c r="J47" s="42"/>
     </row>
     <row r="48" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="49" ht="45" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="56" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="Q7:Q8"/>
-    <mergeCell ref="R7:R8"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="M7:M8"/>
-    <mergeCell ref="N7:N8"/>
-    <mergeCell ref="O7:O8"/>
-    <mergeCell ref="P7:P8"/>
-    <mergeCell ref="A43:C46"/>
-    <mergeCell ref="D43:F46"/>
-    <mergeCell ref="G43:J46"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="G47:J47"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="A41:K41"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="G42:J42"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:F3"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="H5:I5"/>
     <mergeCell ref="A6:B6"/>
@@ -2352,13 +2340,25 @@
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="E7:J7"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="A41:K41"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="G42:J42"/>
+    <mergeCell ref="A43:C46"/>
+    <mergeCell ref="D43:F46"/>
+    <mergeCell ref="G43:J46"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="G47:J47"/>
+    <mergeCell ref="Q7:Q8"/>
+    <mergeCell ref="R7:R8"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="M7:M8"/>
+    <mergeCell ref="N7:N8"/>
+    <mergeCell ref="O7:O8"/>
+    <mergeCell ref="P7:P8"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.5" footer="0.5"/>
